--- a/weather.xlsx
+++ b/weather.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>timestamp</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,6 +492,7 @@
           <t>2026-06-14 09:07:21</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -515,6 +521,69 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-14 09:07:33</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1021</v>
+      </c>
+      <c r="F4" t="n">
+        <v>63</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:21:15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1021</v>
+      </c>
+      <c r="F5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:26:38</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
         </is>
       </c>
     </row>
